--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_378D6A058A9F91899D452DB55D797FAAC148EC5D" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{03F9492C-5135-4AA6-89B8-766B59368CF5}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="194">
   <si>
     <t>49018</t>
   </si>
@@ -127,18 +133,42 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>BB47D66ED0F0C10E8EB6F1452CD564DB</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>01/10/2022</t>
+  </si>
+  <si>
+    <t>31/12/2022</t>
+  </si>
+  <si>
+    <t>Catálogo de disposición documental</t>
+  </si>
+  <si>
+    <t>https://platrans.tlaxcala.gob.mx/sistemas/trans2016/view_cambios.php?_sess=cetra15488747231729&amp;recno=37790</t>
+  </si>
+  <si>
+    <t>2693722</t>
+  </si>
+  <si>
+    <t>Unidad de Transparencia</t>
+  </si>
+  <si>
+    <t>24/01/2022</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>AE5E440103256CB9AA342C48907BFF85</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>01/04/2022</t>
   </si>
   <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
     <t>Cuadro general de clasificación archivística</t>
   </si>
   <si>
@@ -154,43 +184,25 @@
     <t>13/01/2023</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>2821934</t>
-  </si>
-  <si>
-    <t>Catálogo de disposición documental</t>
-  </si>
-  <si>
-    <t>2693722</t>
-  </si>
-  <si>
-    <t>645112</t>
-  </si>
-  <si>
-    <t>885140</t>
-  </si>
-  <si>
-    <t>1626790</t>
-  </si>
-  <si>
-    <t>1848767</t>
-  </si>
-  <si>
-    <t>2079885</t>
-  </si>
-  <si>
-    <t>1353810</t>
-  </si>
-  <si>
-    <t>3012233</t>
-  </si>
-  <si>
-    <t>3012234</t>
-  </si>
-  <si>
-    <t>3012235</t>
+    <t>6CABD97CC31D1CE40C25F807ED8FDDBB</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>8547378</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/01/2024</t>
   </si>
   <si>
     <t>Dictamen y acta de baja documental y transferencia secundaria</t>
@@ -244,12 +256,30 @@
     <t>Segundo apellido</t>
   </si>
   <si>
-    <t>Puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Cargo</t>
   </si>
   <si>
+    <t>AA35CD2ECFE09A8282675F758CA7EBA6</t>
+  </si>
+  <si>
+    <t>EDUARDO ANTONIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BETANCOUR</t>
+  </si>
+  <si>
+    <t>RESPONSABLE DEL AREA</t>
+  </si>
+  <si>
+    <t>JEFE DE OFICINA</t>
+  </si>
+  <si>
     <t>BE35470518298479E79AB503FA493C35</t>
   </si>
   <si>
@@ -268,97 +298,322 @@
     <t>Encargado de la Unidad de Transparencia y Archivo</t>
   </si>
   <si>
-    <t>8FE95E98D67ED6547CD2DDBA4F26EBD5</t>
-  </si>
-  <si>
-    <t>Antonio Eduardo</t>
-  </si>
-  <si>
-    <t>Jefe de Mataria</t>
-  </si>
-  <si>
-    <t>Responsable de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>AA35CD2ECFE09A8282675F758CA7EBA6</t>
-  </si>
-  <si>
-    <t>EDUARDO ANTONIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>BETANCOUR</t>
-  </si>
-  <si>
-    <t>RESPONSABLE DEL AREA</t>
-  </si>
-  <si>
-    <t>JEFE DE OFICINA</t>
-  </si>
-  <si>
-    <t>8F812EA806798BC1651FA105A9E29BB9</t>
-  </si>
-  <si>
-    <t>Zurisadai</t>
+    <t>70B8A9CB5BBA63C19891D5A4BDA29E44</t>
+  </si>
+  <si>
+    <t>Librado</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdireccion de Planeación y Evaluacion</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C1546E613E2BCBFF31</t>
+  </si>
+  <si>
+    <t>Aquina</t>
+  </si>
+  <si>
+    <t>Castañeda</t>
+  </si>
+  <si>
+    <t>Romero</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Deparetamento de Planeacion</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C19CC781D256891282</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>Netzahuatl</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de Departamento de Planes y Programas</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C1A4A2E6696A8424EE</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Flores</t>
   </si>
   <si>
     <t>Guzman</t>
   </si>
   <si>
-    <t>2A0D01CFAE2F91AC551DB3D92EA2F975</t>
+    <t>Responsable del archivo de trámite de Departameto de Relaciones Públicas</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C110AE86AEE1524FF5</t>
+  </si>
+  <si>
+    <t>Yeraldi</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
   </si>
   <si>
     <t>Juarez</t>
   </si>
   <si>
-    <t>Responsable de la Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>Capturista</t>
-  </si>
-  <si>
-    <t>785013A4D09C419F11771D1EBA4BB3AB</t>
-  </si>
-  <si>
-    <t>3EA40E1D964DE660086694F473156C90</t>
-  </si>
-  <si>
-    <t>56A4AF979F0554F2FD5E20C2E9EA6365</t>
-  </si>
-  <si>
-    <t>Surisadai</t>
-  </si>
-  <si>
-    <t>35CA7E5D86D05B6CDD40C89B14123758</t>
-  </si>
-  <si>
-    <t>ED39F626C58EF0044627FEA2A4BDE1C8</t>
-  </si>
-  <si>
-    <t>Nestor</t>
-  </si>
-  <si>
-    <t>Ahuatzi</t>
-  </si>
-  <si>
-    <t>Flores</t>
-  </si>
-  <si>
-    <t>Jefe de Oficina</t>
-  </si>
-  <si>
-    <t>515868DA600EBA8387204785EBC6155A</t>
-  </si>
-  <si>
-    <t>BBEE0012F9AB75BDDDA074AD2E5125AA</t>
+    <t>Responsable del archivo de trámite de  Dirección Académica</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C1EDD61C66DBA00CB0</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>Cuateconzi</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de  Subdirección Juridica</t>
+  </si>
+  <si>
+    <t>70B8A9CB5BBA63C1965B094D95CEDD6D</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Bonilla</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C586BF66F10B7B004C</t>
+  </si>
+  <si>
+    <t>Ibrail Oswaldo</t>
+  </si>
+  <si>
+    <t>Fernandez</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdirección  de Seguimiento Academico</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C5AC5303B1AF6FA8EA</t>
+  </si>
+  <si>
+    <t>Fabiola</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdirección de Paraescolares</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C51AC830B085CF1FD1</t>
+  </si>
+  <si>
+    <t>Ivonne</t>
+  </si>
+  <si>
+    <t>Portillo</t>
+  </si>
+  <si>
+    <t>Nava</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Dirección General</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C5EDC4D6B4DCA5EE29</t>
+  </si>
+  <si>
+    <t>Eloisa</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>Aguila</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Bibliotecas y Laboratorios</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C5917F92CDD4237FBE</t>
+  </si>
+  <si>
+    <t>Leticia</t>
+  </si>
+  <si>
+    <t>Palacios</t>
+  </si>
+  <si>
+    <t>Toquianzi</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del  Departameto de Orientacion Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C5E48AF5822AB77EA7</t>
+  </si>
+  <si>
+    <t>Viridiana</t>
+  </si>
+  <si>
+    <t>Meneses</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C51BBED07002A33C97</t>
+  </si>
+  <si>
+    <t>Karla Sidoni</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Dirección Administrativa</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C50BBAC7745D2269C4</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>Romano</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C56FFE332AAB62BC2F</t>
+  </si>
+  <si>
+    <t>Vircey</t>
+  </si>
+  <si>
+    <t>Diyarza</t>
+  </si>
+  <si>
+    <t>Meza</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>02F12D71DE2231C5A475FF99DFB95742</t>
+  </si>
+  <si>
+    <t>Yohana Moraima</t>
+  </si>
+  <si>
+    <t>Bautista</t>
+  </si>
+  <si>
+    <t>Reyes</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>818F557B9177A21BE9C5FB94B37643A2</t>
+  </si>
+  <si>
+    <t>Fabián</t>
+  </si>
+  <si>
+    <t>Castro</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Area de Sistemas y Organización</t>
+  </si>
+  <si>
+    <t>818F557B9177A21BDE5A5B6F2789B5AF</t>
+  </si>
+  <si>
+    <t>Narda Susana</t>
+  </si>
+  <si>
+    <t>Limon</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite de la Subdirección Administrativa</t>
+  </si>
+  <si>
+    <t>818F557B9177A21BFD45E12933587D1E</t>
+  </si>
+  <si>
+    <t>Maria del Socorro</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>818F557B9177A21BD4DBB7AF6588ECC1</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Toquiantzi</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de trámite del Departamento de Recursos Materiales</t>
+  </si>
+  <si>
+    <t>818F557B9177A21B41AC5A5FCF73B4FB</t>
+  </si>
+  <si>
+    <t>Yolanda</t>
+  </si>
+  <si>
+    <t>Briones</t>
+  </si>
+  <si>
+    <t>Responsable del archivo de la Contraloria Interna</t>
+  </si>
+  <si>
+    <t>818F557B9177A21BA55D47314582DFE5</t>
+  </si>
+  <si>
+    <t>Marishely</t>
+  </si>
+  <si>
+    <t>Jimenez</t>
+  </si>
+  <si>
+    <t>Responsable del archivo del Departamento de Inventarios</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -457,6 +712,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -472,44 +730,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -537,14 +795,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -572,6 +847,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -583,175 +875,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -947,6 +1215,76 @@
         <v>44</v>
       </c>
     </row>
+    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:K6"/>
@@ -958,7 +1296,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E178">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -967,58 +1305,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1027,17 +1365,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1059,40 +1397,40 @@
     </row>
     <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1100,252 +1438,252 @@
         <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1353,22 +1691,321 @@
         <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>108</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
